--- a/output/pdf_financials_xlsx/X.xlsx
+++ b/output/pdf_financials_xlsx/X.xlsx
@@ -6823,16 +6823,16 @@
         <v>0</v>
       </c>
       <c r="D126" s="3" t="n">
-        <v>0</v>
+        <v>-5.3</v>
       </c>
       <c r="E126" s="3" t="n">
-        <v>0</v>
+        <v>-3.3</v>
       </c>
       <c r="F126" s="3" t="n">
-        <v>0</v>
+        <v>-1.3</v>
       </c>
       <c r="G126" s="3" t="n">
-        <v>0</v>
+        <v>-3.4</v>
       </c>
       <c r="H126" s="3" t="n">
         <v>0</v>
@@ -6847,16 +6847,16 @@
         <v>0</v>
       </c>
       <c r="L126" s="3" t="n">
-        <v>0</v>
+        <v>-25.5</v>
       </c>
       <c r="M126" s="3" t="n">
-        <v>0</v>
+        <v>-33.3</v>
       </c>
       <c r="N126" s="3" t="n">
-        <v>0</v>
+        <v>-38.5</v>
       </c>
       <c r="O126" s="3" t="n">
-        <v>0</v>
+        <v>-81.7</v>
       </c>
     </row>
     <row r="127">
@@ -53132,7 +53132,11 @@
           <t>Dividends paid to non-controlling interests 26</t>
         </is>
       </c>
-      <c r="D542" t="inlineStr"/>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>CashDividendsPaid</t>
+        </is>
+      </c>
       <c r="E542" t="inlineStr">
         <is>
           <t>-</t>
@@ -54728,7 +54732,11 @@
           <t>Dividends paid to non-controlling interests 3</t>
         </is>
       </c>
-      <c r="D562" t="inlineStr"/>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>CashDividendsPaid</t>
+        </is>
+      </c>
       <c r="E562" t="inlineStr">
         <is>
           <t>-</t>
@@ -61292,7 +61300,11 @@
           <t>Dividend paid to non-controlling interests</t>
         </is>
       </c>
-      <c r="D641" t="inlineStr"/>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>CashDividendsPaid</t>
+        </is>
+      </c>
       <c r="E641" t="inlineStr">
         <is>
           <t>-</t>
@@ -68122,7 +68134,11 @@
           <t>BOX dividend paid to non-controlling interest</t>
         </is>
       </c>
-      <c r="D722" t="inlineStr"/>
+      <c r="D722" t="inlineStr">
+        <is>
+          <t>CashDividendsPaid</t>
+        </is>
+      </c>
       <c r="E722" t="inlineStr">
         <is>
           <t>-</t>
@@ -68720,7 +68736,11 @@
           <t>Additions to intangible assets 11</t>
         </is>
       </c>
-      <c r="D729" t="inlineStr"/>
+      <c r="D729" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E729" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/X.xlsx
+++ b/output/pdf_financials_xlsx/X.xlsx
@@ -2329,7 +2329,7 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>0</v>
+        <v>80.7</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>83.59999999999999</v>
@@ -2482,10 +2482,10 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>0</v>
+        <v>12.3</v>
       </c>
       <c r="E40" s="3" t="n">
         <v>0</v>
@@ -2533,10 +2533,10 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>0</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>83.59999999999999</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="E41" s="3" t="n">
         <v>91.3</v>
@@ -2890,7 +2890,7 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>17.2</v>
@@ -3480,37 +3480,37 @@
         <v>0</v>
       </c>
       <c r="D59" s="3" t="n">
-        <v>4806.9</v>
+        <v>0</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>4650.3</v>
+        <v>0</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>4399.7</v>
+        <v>0</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>4319.8</v>
+        <v>0</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>5067.6</v>
+        <v>0</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>5054.9</v>
+        <v>0</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>5041.2</v>
+        <v>0</v>
       </c>
       <c r="K59" s="3" t="n">
-        <v>5156.9</v>
+        <v>0</v>
       </c>
       <c r="L59" s="3" t="n">
-        <v>5517.6</v>
+        <v>0</v>
       </c>
       <c r="M59" s="3" t="n">
-        <v>5499.5</v>
+        <v>0</v>
       </c>
       <c r="N59" s="3" t="n">
-        <v>7315.2</v>
+        <v>0</v>
       </c>
       <c r="O59" s="3" t="n">
         <v>0</v>
@@ -3879,16 +3879,14 @@
           <t xml:space="preserve">    Current Accrued Expense</t>
         </is>
       </c>
-      <c r="B67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B67" s="3" t="n">
+        <v>11.6</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>13.1</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>28.8</v>
       </c>
       <c r="E67" s="3" t="n">
         <v>0</v>
@@ -3936,10 +3934,10 @@
         </is>
       </c>
       <c r="C68" s="3" t="n">
-        <v>0</v>
+        <v>13.1</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>104.9</v>
+        <v>133.7</v>
       </c>
       <c r="E68" s="3" t="n">
         <v>77.09999999999999</v>
@@ -5942,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="E108" s="3" t="n">
-        <v>0</v>
+        <v>136.1</v>
       </c>
       <c r="F108" s="3" t="n">
-        <v>0</v>
+        <v>221.7</v>
       </c>
       <c r="G108" s="3" t="n">
         <v>0</v>
@@ -5957,7 +5955,7 @@
         <v>0</v>
       </c>
       <c r="J108" s="3" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="K108" s="3" t="n">
         <v>0</v>
@@ -12268,7 +12266,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>OtherIntangibleAssets</t>
+          <t>GoodwillAndOtherIntangibleAssets</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -14780,7 +14778,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>OtherIntangibleAssets</t>
+          <t>GoodwillAndOtherIntangibleAssets</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -23460,7 +23458,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>OtherIntangibleAssets</t>
+          <t>GoodwillAndOtherIntangibleAssets</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -27200,7 +27198,7 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>OtherIntangibleAssets</t>
+          <t>GoodwillAndOtherIntangibleAssets</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -31462,7 +31460,7 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>OtherIntangibleAssets</t>
+          <t>GoodwillAndOtherIntangibleAssets</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -56298,7 +56296,11 @@
           <t>Impairment charges 17</t>
         </is>
       </c>
-      <c r="D581" t="inlineStr"/>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>AssetImpairmentCharge</t>
+        </is>
+      </c>
       <c r="E581" t="inlineStr">
         <is>
           <t>-</t>
@@ -63986,7 +63988,11 @@
           <t>Impairment charges 11</t>
         </is>
       </c>
-      <c r="D673" t="inlineStr"/>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>AssetImpairmentCharge</t>
+        </is>
+      </c>
       <c r="E673" t="inlineStr">
         <is>
           <t>-</t>
@@ -65500,7 +65506,11 @@
           <t>Impairment charges 9</t>
         </is>
       </c>
-      <c r="D691" t="inlineStr"/>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>AssetImpairmentCharge</t>
+        </is>
+      </c>
       <c r="E691" t="inlineStr">
         <is>
           <t>-</t>
